--- a/Report/ReportLogin.xlsx
+++ b/Report/ReportLogin.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ppham\Documents\Do an\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ppham\Documents\Do an\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904B33B3-06EB-47CB-832C-6508077F2927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B4E9F5-0600-464D-B10C-BC4DF1096811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2F9B1718-7680-4F4C-BE2C-0BB9EDB9855F}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -121,7 +121,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -146,14 +145,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -209,8 +210,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent1" xfId="2" builtinId="29"/>
@@ -530,13 +531,17 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="20.21875"/>
-    <col min="3" max="3" customWidth="true" width="12.77734375"/>
-    <col min="4" max="4" customWidth="true" width="36.88671875"/>
-    <col min="5" max="5" customWidth="true" width="26.0"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="15.77734375" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,17 +557,17 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="4">
+      <c r="F1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G1" t="s" s="4">
+      <c r="G1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H1" t="s" s="4">
+      <c r="H1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -578,17 +583,17 @@
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -604,17 +609,17 @@
       <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s" s="0">
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" t="s" s="0">
+      <c r="H3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -630,17 +635,17 @@
       <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s" s="0">
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
         <v>11</v>
       </c>
-      <c r="H4" t="s" s="0">
+      <c r="H4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -654,17 +659,17 @@
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s" s="0">
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="H5" t="s" s="0">
+      <c r="H5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -678,17 +683,17 @@
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F6" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="G6" t="s" s="0">
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
         <v>14</v>
       </c>
-      <c r="H6" t="s" s="0">
+      <c r="H6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -700,45 +705,45 @@
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F7" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="G7" t="s" s="0">
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
         <v>14</v>
       </c>
-      <c r="H7" t="s" s="0">
+      <c r="H7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="s" s="5">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="s" s="5">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="s" s="5">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="s" s="5">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="B12" t="s">
         <v>29</v>
       </c>
     </row>
